--- a/backend/src/main/resources/data/policy_final_data.xlsx
+++ b/backend/src/main/resources/data/policy_final_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeonsangmin/Desktop/공모전/backend/src/main/resources/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB706854-A91F-064A-8F67-B82CDEF6128C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA24ED7F-CB92-8B48-A102-BBECB219894A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="청년정책" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">청년정책!$A$1:$AC$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">청년정책!$A$1:$AC$526</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13127" uniqueCount="3627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13150" uniqueCount="3645">
   <si>
     <t>정책명</t>
   </si>
@@ -14184,6 +14184,62 @@
   </si>
   <si>
     <t>https://www.korea.kr</t>
+  </si>
+  <si>
+    <t>청년월세지원사업</t>
+  </si>
+  <si>
+    <t>REAL_POLICY_002</t>
+  </si>
+  <si>
+    <t>주거</t>
+  </si>
+  <si>
+    <t>월세,주거지원,청년독립</t>
+  </si>
+  <si>
+    <t>청년의 주거비 부담 완화를 지원하는 정책입니다.</t>
+  </si>
+  <si>
+    <t>경제적 어려움을 겪는 청년에게 월세 일부를 지원하여 안정적인 주거 환경을 제공합니다.</t>
+  </si>
+  <si>
+    <t>예산 소진 시까지</t>
+  </si>
+  <si>
+    <t>중위소득 150% 이하</t>
+  </si>
+  <si>
+    <t>소득 기준 충족 필요</t>
+  </si>
+  <si>
+    <t>무주택 청년 우대</t>
+  </si>
+  <si>
+    <t>부모와 별도 거주 필요</t>
+  </si>
+  <si>
+    <t>복지로 및 지자체 홈페이지 신청</t>
+  </si>
+  <si>
+    <t>소득 및 거주 요건 심사</t>
+  </si>
+  <si>
+    <t>주민등록등본, 임대차계약서, 소득증빙서류</t>
+  </si>
+  <si>
+    <t>청년의 월세 부담을 줄여 안정적인 자립 기반 마련을 지원하는 사업입니다.</t>
+  </si>
+  <si>
+    <t>https://www.molit.go.kr</t>
+  </si>
+  <si>
+    <t>인천광역시</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>인천광역시 계양구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -14285,7 +14341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -14303,6 +14359,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -61297,7 +61356,7 @@
         <v>3613</v>
       </c>
       <c r="L525" t="s">
-        <v>441</v>
+        <v>3643</v>
       </c>
       <c r="M525" s="6" t="s">
         <v>3614</v>
@@ -61352,7 +61411,93 @@
       </c>
     </row>
     <row r="526" spans="1:29">
-      <c r="M526" s="6"/>
+      <c r="A526" t="s">
+        <v>3627</v>
+      </c>
+      <c r="B526" t="s">
+        <v>3628</v>
+      </c>
+      <c r="C526" t="s">
+        <v>3629</v>
+      </c>
+      <c r="D526" t="s">
+        <v>3630</v>
+      </c>
+      <c r="E526" t="s">
+        <v>3631</v>
+      </c>
+      <c r="F526" t="s">
+        <v>3632</v>
+      </c>
+      <c r="G526" s="5">
+        <v>46054</v>
+      </c>
+      <c r="H526" s="5">
+        <v>46387</v>
+      </c>
+      <c r="I526" s="5">
+        <v>46054</v>
+      </c>
+      <c r="J526" s="5">
+        <v>46387</v>
+      </c>
+      <c r="K526" t="s">
+        <v>3633</v>
+      </c>
+      <c r="L526" s="4" t="s">
+        <v>3644</v>
+      </c>
+      <c r="M526" s="7" t="s">
+        <v>3634</v>
+      </c>
+      <c r="N526" t="s">
+        <v>39</v>
+      </c>
+      <c r="O526">
+        <v>19</v>
+      </c>
+      <c r="P526">
+        <v>34</v>
+      </c>
+      <c r="Q526" t="s">
+        <v>38</v>
+      </c>
+      <c r="R526" t="s">
+        <v>3635</v>
+      </c>
+      <c r="S526" t="s">
+        <v>3636</v>
+      </c>
+      <c r="T526" t="s">
+        <v>39</v>
+      </c>
+      <c r="U526" t="s">
+        <v>3637</v>
+      </c>
+      <c r="V526" t="s">
+        <v>3620</v>
+      </c>
+      <c r="W526" t="s">
+        <v>3638</v>
+      </c>
+      <c r="X526" t="s">
+        <v>3639</v>
+      </c>
+      <c r="Y526" t="s">
+        <v>3640</v>
+      </c>
+      <c r="Z526" t="s">
+        <v>414</v>
+      </c>
+      <c r="AA526" t="s">
+        <v>3641</v>
+      </c>
+      <c r="AB526" t="s">
+        <v>3642</v>
+      </c>
+      <c r="AC526" t="s">
+        <v>3626</v>
+      </c>
     </row>
     <row r="527" spans="1:29">
       <c r="M527" s="6"/>
@@ -61369,7 +61514,7 @@
       <c r="M530" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AC526" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
